--- a/artfynd/A 2536-2020 artfynd.xlsx
+++ b/artfynd/A 2536-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117772797</v>
       </c>
       <c r="B2" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>117772842</v>
       </c>
       <c r="B3" t="n">
-        <v>101199</v>
+        <v>101201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>117772790</v>
       </c>
       <c r="B4" t="n">
-        <v>100097</v>
+        <v>100099</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
